--- a/outputs/evaluation/architecture/validation/gemini-3-5/CF_M06/run_2/CF_M06_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/validation/gemini-3-5/CF_M06/run_2/CF_M06_arch_eval.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,6 +440,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -456,7 +461,10 @@
       <c r="C2" t="n">
         <v>0.6389</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>0.5227000000000001</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -475,6 +483,9 @@
         <v>0.7241</v>
       </c>
       <c r="D3" t="n">
+        <v>0.5455</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.979</v>
       </c>
     </row>
@@ -491,6 +502,9 @@
         <v>0.2857</v>
       </c>
       <c r="D4" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.8953</v>
       </c>
     </row>
@@ -1226,13 +1240,11 @@
           <t>['P_03']</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>P_04</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>Observer Pattern</t>
@@ -1256,13 +1268,11 @@
           <t>CF_M06_P02</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>CF_M06_P03</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1303,14 +1313,11 @@
           <t>48</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>P_05</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Decorator Pattern</t>
@@ -1334,13 +1341,11 @@
           <t>CF_M06_AU23</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>CF_M06_P04</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1361,7 +1366,6 @@
       <c r="D4" t="n">
         <v>0.8668</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1382,7 +1386,6 @@
           <t>['AU_07', 'AU_08']</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>AU_43</t>
@@ -1393,7 +1396,6 @@
           <t>dispositiu mòbil, waapiti servidor</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1412,7 +1414,6 @@
           <t>CF_M06_AU01, CF_M06_AU02</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>CF_M06_AU27</t>
@@ -1463,14 +1464,11 @@
           <t>44</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>AU_08</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Waapiti Server</t>
@@ -1489,14 +1487,11 @@
       <c r="P5" t="n">
         <v>45</v>
       </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>CF_M06_AU02</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1517,7 +1512,6 @@
       <c r="D6" t="n">
         <v>0.9237</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1538,7 +1532,6 @@
           <t>['AU_08', 'AU_11', 'AU_35']</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>AU_44</t>
@@ -1549,7 +1542,6 @@
           <t>waapiti servidor, dades, aws</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1568,7 +1560,6 @@
           <t>CF_M06_AU02, CF_M06_AU05</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>CF_M06_AU28</t>
@@ -1619,14 +1610,11 @@
           <t>45</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>AU_16</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>React Native</t>
@@ -1650,13 +1638,11 @@
           <t>CF_M06_AU23</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>CF_M06_AU06</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1697,14 +1683,11 @@
           <t>45</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>AU_17</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>React</t>
@@ -1728,13 +1711,11 @@
           <t>CF_M06_AU23</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>CF_M06_AU14</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1775,14 +1756,11 @@
           <t>48</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>P_06</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Lazy Loading</t>
@@ -1806,13 +1784,11 @@
           <t>CF_M06_AU23</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>CF_M06_P05</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1853,14 +1829,11 @@
           <t>46</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>AU_14</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Dispatcher</t>
@@ -1884,13 +1857,11 @@
           <t>CF_M06_P02</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>CF_M06_AU09</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1931,14 +1902,11 @@
           <t>50</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>AU_20</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Jest</t>
@@ -1962,13 +1930,11 @@
           <t>CF_M06_AU23</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>CF_M06_AU16</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2014,13 +1980,11 @@
           <t>['AU_43']</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>AU_34</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>HTTP</t>
@@ -2044,13 +2008,11 @@
           <t>CF_M06_AU26</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>CF_M06_AU29</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2091,14 +2053,11 @@
           <t>45</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>AU_12</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>Store</t>
@@ -2122,13 +2081,11 @@
           <t>CF_M06_P02</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>CF_M06_AU07</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2169,14 +2126,11 @@
           <t>50</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>AU_19</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>Expo</t>
@@ -2200,13 +2154,11 @@
           <t>CF_M06_AU23</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>CF_M06_AU15</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2247,14 +2199,11 @@
           <t>50</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>AU_21</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>NodeJS</t>
@@ -2273,14 +2222,11 @@
       <c r="P15" t="n">
         <v>51</v>
       </c>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>CF_M06_AU17</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2321,14 +2267,11 @@
           <t>51</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>AU_23</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>NestJS</t>
@@ -2347,14 +2290,11 @@
       <c r="P16" t="n">
         <v>51</v>
       </c>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>CF_M06_AU19</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2395,14 +2335,11 @@
           <t>46</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>AU_18</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>Redux</t>
@@ -2426,13 +2363,11 @@
           <t>CF_M06_AU23</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>CF_M06_AU25</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2478,13 +2413,11 @@
           <t>['AU_32']</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>AU_33</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>AWS SNS</t>
@@ -2503,14 +2436,11 @@
       <c r="P18" t="n">
         <v>92</v>
       </c>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>CF_M06_AU22</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2551,14 +2481,11 @@
           <t>45</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>P_03</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>Flux</t>
@@ -2582,13 +2509,11 @@
           <t>CF_M06_AU23</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>CF_M06_P02</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2634,13 +2559,11 @@
           <t>['AU_29', 'AU_45']</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>AU_31</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>Apple Push Notification Service</t>
@@ -2659,14 +2582,11 @@
       <c r="P20" t="n">
         <v>91</v>
       </c>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>CF_M06_AU21</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2707,14 +2627,11 @@
           <t>44</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>P_02</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>Three Layers</t>
@@ -2738,13 +2655,11 @@
           <t>CF_M06_AU23</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>CF_M06_P01</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2790,13 +2705,11 @@
           <t>['AU_29', 'AU_45']</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>AU_30</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>Firebase Cloud Messaging</t>
@@ -2815,14 +2728,11 @@
       <c r="P22" t="n">
         <v>91</v>
       </c>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>CF_M06_AU20</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2863,14 +2773,11 @@
           <t>46</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>AU_13</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>Action</t>
@@ -2894,13 +2801,11 @@
           <t>CF_M06_P02</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
           <t>CF_M06_AU08</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2941,14 +2846,11 @@
           <t>50</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>AU_22</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>TypeScript</t>
@@ -2967,14 +2869,11 @@
       <c r="P24" t="n">
         <v>51</v>
       </c>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>CF_M06_AU18</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3048,7 +2947,6 @@
           <t>Client</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>L’empresa t´ e dues vies de negoci. D’altra banda, treballa amb partners, que essencialment s´ on empreses de tercers que disposen dels seus propis clients i els hi ofereixen solucions de senyalitzaci´ o digital mitjan¸ cant la tecnologia de Waapiti.</t>
@@ -3084,7 +2982,6 @@
           <t>Players</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Players: s´ on equips inform` atics que fan la funci´ o d’intermediari entre la plataforma de Waapiti i el suport audiovisual en si, permetent aix´ ı la sincronitzaci´ o i reproducci´ o dels continguts dels clients.</t>
@@ -3120,7 +3017,6 @@
           <t>Monitors LCD</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Aquesta nova tecnologia pret´ en substituir els cartells tradicionals oferint una millora en la presentaci´ o i promoci´ o de productes. L’objectiu ´ es crear una xarxa de sistemes audiovisuals amb continguts di` ariament actualitzats. Un exemple de cas d’´ us podria ser una xarxa de pantalles per franqu´ ıcies (supermercat).</t>
@@ -3156,7 +3052,6 @@
           <t>Pantalles de plasma</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>Aquesta nova tecnologia pret´ en substituir els cartells tradicionals oferint una millora en la presentaci´ o i promoci´ o de productes. L’objectiu ´ es crear una xarxa de sistemes audiovisuals amb continguts di` ariament actualitzats.</t>
@@ -3192,7 +3087,6 @@
           <t>Panells de LED</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Aquesta nova tecnologia pret´ en substituir els cartells tradicionals oferint una millora en la presentaci´ o i promoci´ o de productes. L’objectiu ´ es crear una xarxa de sistemes audiovisuals amb continguts di` ariament actualitzats.</t>
@@ -3228,7 +3122,6 @@
           <t>Projectors</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Aquesta nova tecnologia pret´ en substituir els cartells tradicionals oferint una millora en la presentaci´ o i promoci´ o de productes. L’objectiu ´ es crear una xarxa de sistemes audiovisuals amb continguts di` ariament actualitzats.</t>
@@ -3264,7 +3157,6 @@
           <t>Dispositiu mòbil</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>L’arquitectura f´ ısica de la soluci´ o est` a format per un dispositiu m` obil, ja sigui sistema iOS o Android, i el servidor de l’empresa.</t>
@@ -3300,7 +3192,6 @@
           <t>Presentació</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Presentaci´ o:´ es la capa que es comunica amb l’usuari. En aquest es mostra les dades del sistema i es recullen les dades introdu¨ ıdes per l’usuari. En aquest cas, la capa de presentaci´ o ´ es l’aplicaci´ o m` obil.</t>
@@ -3336,7 +3227,6 @@
           <t>Domini</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>Domini: ´ es la capa que cont´ e la l` ogica de negoci. En aquest es processa la informaci´ o i es realitzen les operacions necess` aries per a que el sistema funcioni correctament.</t>
@@ -3372,7 +3262,6 @@
           <t>Dades</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Dades: ´ es la capa que cont´ e la informaci´ o.</t>
@@ -3408,7 +3297,6 @@
           <t>Reducers</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>Els canvis es fan amb funcions pures: els Reducers s´ on funcions pures que reben l’estat actual de l’aplicaci´ o i l’acci´ o a realitzar i retornen un nou estat, sense modificar directament l’estat actual.</t>
@@ -3444,7 +3332,6 @@
           <t>Visual Studio Code</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>Visual Studio Code: ´ es un editor de codi font desenvolupar per Microsoft.</t>
@@ -3480,7 +3367,6 @@
           <t>GIT</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>GIT: ´ es un sistema de control de versions de codi font.</t>
@@ -3516,7 +3402,6 @@
           <t>React Navigation</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>Per a la navegaci´ o s’utilitza la llibreria React Navigation, que ofereix la transici´ o entre pantalles de forma senzilla i un historial de navegaci´ o.</t>
@@ -3552,7 +3437,6 @@
           <t>react-native-async-storage</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>Per a la gesti´ o de la sessi´ o s’utilitza la llibreria react-native-async-storage, que ens permet guardar parells de clau-valor de manera local en els dispositius.</t>
@@ -3588,7 +3472,6 @@
           <t>expo-notifications</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>Per rebre les notificacions s’utilitza la llibreria expo-notifications el qual ofereix una API per a la gesti´ o de notificacions.</t>
@@ -3624,7 +3507,6 @@
           <t>Messaging Service</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>Per poder implementar aquesta funcionalitat ´ es necessari utilitzar un servei de missatgeria per cada plataforma: Firebase Cloud Messaging (FCM) per dispositius Android i Apple Push Notification Service (APNS) per dispositius iOS.</t>
@@ -3660,7 +3542,6 @@
           <t>Notification Service</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>Aix´ ı mateix es necessita un servei de notificacions que es comuniqui amb aquestes. Com a conseq¨ u` encia es va fer un estudi sobre diferents alternatives: Expo Push API i AWS SNS.</t>
@@ -3696,7 +3577,6 @@
           <t>AWS</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>Es el servidor que s’encarrega de comunicar-se amb la base de dades i altres serveis allotjats a AWS.</t>
@@ -3732,7 +3612,6 @@
           <t>Google Maps</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>S’utilitza l’API de Google Maps per tal de facilitar la b´ usqueda d’adre¸ ca, facilitant aix´ ı la feina a l’hora d’omplir camps de formulari</t>
@@ -3768,7 +3647,6 @@
           <t>Expo Push API</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>Expo Push API ´ es un servei que facilita la implementaci´ o de les notificacions push ja que es delega tota la configuraci´ o al servei.</t>
@@ -3804,7 +3682,6 @@
           <t>iOS</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>L’aplicaci´ o ha d’estar disponible per dispositius m` obils amb sistema iOS i Android</t>
@@ -3840,7 +3717,6 @@
           <t>Android</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>L’aplicaci´ o ha d’estar disponible per dispositius m` obils amb sistema iOS i Android</t>
@@ -3876,7 +3752,6 @@
           <t>Javascript</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>React ´ es una llibreria per construir interf´ ıcies d’usuari utilitzant Javascript.</t>
@@ -3912,7 +3787,6 @@
           <t>Google Play Store</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>Es pot descarregar-se des de Google Play Store, en cas d’Android...</t>
@@ -3948,7 +3822,6 @@
           <t>App Store</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>...i des de l’App Store, en cas d’iOS.</t>
@@ -3979,7 +3852,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>messaging service, ios, android</t>
@@ -4015,7 +3887,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
           <t>notification service, messaging service</t>
@@ -4056,7 +3927,6 @@
           <t>Client-Server</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>Disposa d’una plataforma escalable, basada en web i sense servidor</t>
@@ -4067,7 +3937,6 @@
           <t>CF_M06_AU30</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
         <v>0.7382</v>
       </c>
@@ -4144,7 +4013,6 @@
           <t>Mobile device</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>This is the device where the application will be hosted.</t>
@@ -4180,7 +4048,6 @@
           <t>Presentation</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>This is the layer that communicates with the user. This is where the system data is displayed and the data entered by the user is collected.</t>
@@ -4216,7 +4083,6 @@
           <t>Domain</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>This is the layer that contains the business logic. In this layer, the information is processed or the operations necessary for the system to function correctly are performed</t>
@@ -4252,7 +4118,6 @@
           <t>Data</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>this is the layer that contains the information.</t>
@@ -4283,7 +4148,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>action, store</t>
@@ -4319,7 +4183,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>dispatcher, store</t>
@@ -4335,7 +4198,6 @@
           <t>AU_44</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>0.6837</v>
       </c>
@@ -4356,7 +4218,6 @@
           <t>User</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>As already mentioned, there are third-party companies that offer digital signage consulting using Waapiti technology. They are end users of this project.</t>
@@ -4387,7 +4248,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>presentation, user</t>
@@ -4428,7 +4288,6 @@
           <t>Mobile Application</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>The project “Development of a mobile application for a digital signage company”</t>
@@ -4464,7 +4323,6 @@
           <t>Player</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t xml:space="preserve">these are computer equipment that act as an intermediary between the Waapiti platform and the audiovisual media itself, thus allowing the synchronization or reproduction of client
@@ -4496,7 +4354,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>waapiti server, mobile application</t>
@@ -4533,7 +4390,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>mobile application, waapiti server</t>
@@ -4574,7 +4430,6 @@
           <t>Socket</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>the content according to the messages that it sends.</t>
